--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/68.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/68.xlsx
@@ -426,13 +426,13 @@
         <v>-5.761704001361107</v>
       </c>
       <c r="E2">
-        <v>-11.91736846618828</v>
+        <v>-15.86494599190191</v>
       </c>
       <c r="F2">
-        <v>-1.579164144146165</v>
+        <v>-2.961001913656549</v>
       </c>
       <c r="G2">
-        <v>-4.063776140457326</v>
+        <v>-3.79567094616213</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.029651185857655</v>
       </c>
       <c r="E3">
-        <v>-12.27623084392142</v>
+        <v>-16.94229316277376</v>
       </c>
       <c r="F3">
-        <v>-1.625714250346483</v>
+        <v>-2.952898823722364</v>
       </c>
       <c r="G3">
-        <v>-3.708088297364053</v>
+        <v>-3.521777731108435</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.426076479128118</v>
       </c>
       <c r="E4">
-        <v>-13.7985696889807</v>
+        <v>-16.60714146849407</v>
       </c>
       <c r="F4">
-        <v>-1.66253186793131</v>
+        <v>-3.051605426705148</v>
       </c>
       <c r="G4">
-        <v>-2.278347961720546</v>
+        <v>-2.825967304174105</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.044577808105858</v>
       </c>
       <c r="E5">
-        <v>-13.50283197017363</v>
+        <v>-16.83656070886628</v>
       </c>
       <c r="F5">
-        <v>-1.489382371561143</v>
+        <v>-3.160264035665164</v>
       </c>
       <c r="G5">
-        <v>-1.430573924371285</v>
+        <v>-2.674742534478459</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.856081494159922</v>
       </c>
       <c r="E6">
-        <v>-14.41845309205666</v>
+        <v>-16.88837617335484</v>
       </c>
       <c r="F6">
-        <v>-1.731836398319128</v>
+        <v>-2.900741498572496</v>
       </c>
       <c r="G6">
-        <v>-1.357995224738335</v>
+        <v>-1.472570361863933</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.848948741810489</v>
       </c>
       <c r="E7">
-        <v>-15.63026878599248</v>
+        <v>-17.90774036092076</v>
       </c>
       <c r="F7">
-        <v>-2.139881068896734</v>
+        <v>-3.353723444017169</v>
       </c>
       <c r="G7">
-        <v>-0.8838030739098381</v>
+        <v>-1.294073754169518</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.972949058918405</v>
       </c>
       <c r="E8">
-        <v>-14.61308088116077</v>
+        <v>-17.98978289743142</v>
       </c>
       <c r="F8">
-        <v>-1.785198998040069</v>
+        <v>-3.020544134202375</v>
       </c>
       <c r="G8">
-        <v>0.3402131986985325</v>
+        <v>-0.9559536114298449</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.190799929514586</v>
       </c>
       <c r="E9">
-        <v>-14.08816896144967</v>
+        <v>-18.36003338061724</v>
       </c>
       <c r="F9">
-        <v>-1.90706758197253</v>
+        <v>-3.43604245467037</v>
       </c>
       <c r="G9">
-        <v>0.1634971188152564</v>
+        <v>-0.454137172082778</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.442878492075175</v>
       </c>
       <c r="E10">
-        <v>-16.74558046158458</v>
+        <v>-18.1417322869616</v>
       </c>
       <c r="F10">
-        <v>-2.121701717874895</v>
+        <v>-3.160322849750763</v>
       </c>
       <c r="G10">
-        <v>0.1544587210408223</v>
+        <v>-0.3576022800817731</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.68769622583902</v>
       </c>
       <c r="E11">
-        <v>-16.1111068271245</v>
+        <v>-18.82243116346702</v>
       </c>
       <c r="F11">
-        <v>-1.664424687446707</v>
+        <v>-2.827630619968815</v>
       </c>
       <c r="G11">
-        <v>1.023831448392364</v>
+        <v>-0.1056549840609766</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.884530846473849</v>
       </c>
       <c r="E12">
-        <v>-15.85071708990305</v>
+        <v>-19.30323182569712</v>
       </c>
       <c r="F12">
-        <v>-0.9456362097917281</v>
+        <v>-2.508960993581456</v>
       </c>
       <c r="G12">
-        <v>1.094655727660085</v>
+        <v>0.3705657153148156</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.00667353466967</v>
       </c>
       <c r="E13">
-        <v>-17.29798664026605</v>
+        <v>-19.9122795004266</v>
       </c>
       <c r="F13">
-        <v>-1.384775307568219</v>
+        <v>-2.405569972935841</v>
       </c>
       <c r="G13">
-        <v>0.598381899079952</v>
+        <v>0.6144458105490721</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.051027142687945</v>
       </c>
       <c r="E14">
-        <v>-17.60723890872411</v>
+        <v>-19.83146631446809</v>
       </c>
       <c r="F14">
-        <v>-0.5018789637446303</v>
+        <v>-1.900281596208796</v>
       </c>
       <c r="G14">
-        <v>0.5809264607437686</v>
+        <v>0.5881843307070636</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.019643236251595</v>
       </c>
       <c r="E15">
-        <v>-19.03262518861659</v>
+        <v>-21.09621053352753</v>
       </c>
       <c r="F15">
-        <v>-0.2445797647610758</v>
+        <v>-2.160556290903206</v>
       </c>
       <c r="G15">
-        <v>1.154162429125331</v>
+        <v>0.2512729627130762</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.937959049642057</v>
       </c>
       <c r="E16">
-        <v>-19.81727894458247</v>
+        <v>-20.57959673004343</v>
       </c>
       <c r="F16">
-        <v>-0.2142068455700291</v>
+        <v>-1.548815247609799</v>
       </c>
       <c r="G16">
-        <v>1.743558906525884</v>
+        <v>0.6570740482327698</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.828268964830849</v>
       </c>
       <c r="E17">
-        <v>-19.31739012310346</v>
+        <v>-21.7489499913942</v>
       </c>
       <c r="F17">
-        <v>0.01691760021986655</v>
+        <v>-1.233476486549098</v>
       </c>
       <c r="G17">
-        <v>0.979025849719678</v>
+        <v>0.8201359339045234</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.720671757814443</v>
       </c>
       <c r="E18">
-        <v>-20.00710977460641</v>
+        <v>-21.67650552625522</v>
       </c>
       <c r="F18">
-        <v>-0.007507641019079672</v>
+        <v>-0.771897744198171</v>
       </c>
       <c r="G18">
-        <v>1.486458000682229</v>
+        <v>0.009452744961208131</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.640349128211878</v>
       </c>
       <c r="E19">
-        <v>-20.87107740724255</v>
+        <v>-22.43302127549539</v>
       </c>
       <c r="F19">
-        <v>0.4597876647785663</v>
+        <v>-0.4807605651776596</v>
       </c>
       <c r="G19">
-        <v>2.194447551134104</v>
+        <v>-0.03701067652683501</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.60091444883101</v>
       </c>
       <c r="E20">
-        <v>-21.45338255425145</v>
+        <v>-23.06082069935647</v>
       </c>
       <c r="F20">
-        <v>0.7758976358912744</v>
+        <v>0.005499383939678165</v>
       </c>
       <c r="G20">
-        <v>1.476926172180075</v>
+        <v>0.04903946519625888</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.618078925058116</v>
       </c>
       <c r="E21">
-        <v>-22.51187414570858</v>
+        <v>-24.81080951676357</v>
       </c>
       <c r="F21">
-        <v>1.315414982069398</v>
+        <v>0.6761887083511035</v>
       </c>
       <c r="G21">
-        <v>1.990799030048903</v>
+        <v>-0.4133077374223573</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.68795343757667</v>
       </c>
       <c r="E22">
-        <v>-22.14398683976659</v>
+        <v>-24.30805082625911</v>
       </c>
       <c r="F22">
-        <v>1.735213357725326</v>
+        <v>0.8822964585764541</v>
       </c>
       <c r="G22">
-        <v>1.522494108273366</v>
+        <v>-0.5475339490852646</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.811211856554493</v>
       </c>
       <c r="E23">
-        <v>-23.30137054607921</v>
+        <v>-24.35040112213838</v>
       </c>
       <c r="F23">
-        <v>1.684687916358973</v>
+        <v>1.189296044993173</v>
       </c>
       <c r="G23">
-        <v>1.080048611672807</v>
+        <v>-0.810905863436773</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.976747915173037</v>
       </c>
       <c r="E24">
-        <v>-23.1285388100078</v>
+        <v>-25.28090735340959</v>
       </c>
       <c r="F24">
-        <v>1.80820080958599</v>
+        <v>0.9600072613678813</v>
       </c>
       <c r="G24">
-        <v>0.8302447369613141</v>
+        <v>-1.132703630992805</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.168519304636878</v>
       </c>
       <c r="E25">
-        <v>-22.40502863116604</v>
+        <v>-25.7911002921855</v>
       </c>
       <c r="F25">
-        <v>2.618378920954824</v>
+        <v>1.621677321497626</v>
       </c>
       <c r="G25">
-        <v>-0.01145931921360929</v>
+        <v>-1.933831494732646</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.376241404038667</v>
       </c>
       <c r="E26">
-        <v>-22.79609916272322</v>
+        <v>-25.5955380305333</v>
       </c>
       <c r="F26">
-        <v>2.233507828470535</v>
+        <v>1.95955844469071</v>
       </c>
       <c r="G26">
-        <v>0.02411990807408257</v>
+        <v>-1.912107488989992</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.577766521938034</v>
       </c>
       <c r="E27">
-        <v>-24.14421909912859</v>
+        <v>-26.41728827005255</v>
       </c>
       <c r="F27">
-        <v>1.86491249871645</v>
+        <v>1.893058766328772</v>
       </c>
       <c r="G27">
-        <v>-0.2749095559028509</v>
+        <v>-2.065047517882</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.763801304764609</v>
       </c>
       <c r="E28">
-        <v>-23.04956549666618</v>
+        <v>-25.92254943061633</v>
       </c>
       <c r="F28">
-        <v>2.53269756701366</v>
+        <v>1.748099441043275</v>
       </c>
       <c r="G28">
-        <v>-0.4879724219836062</v>
+        <v>-2.418618047111881</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.917281109402416</v>
       </c>
       <c r="E29">
-        <v>-22.69376403567945</v>
+        <v>-25.75632960697404</v>
       </c>
       <c r="F29">
-        <v>2.290748016003981</v>
+        <v>1.925076823181778</v>
       </c>
       <c r="G29">
-        <v>0.1083816897522639</v>
+        <v>-2.627354909405161</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.029278506495381</v>
       </c>
       <c r="E30">
-        <v>-23.20052642190105</v>
+        <v>-25.8826827551093</v>
       </c>
       <c r="F30">
-        <v>2.493441235794992</v>
+        <v>1.880253863016297</v>
       </c>
       <c r="G30">
-        <v>-0.6014823753160297</v>
+        <v>-2.553891167355825</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.095031407728678</v>
       </c>
       <c r="E31">
-        <v>-22.94040249020439</v>
+        <v>-25.49812445890945</v>
       </c>
       <c r="F31">
-        <v>1.932409531431359</v>
+        <v>1.880666389982891</v>
       </c>
       <c r="G31">
-        <v>0.9746267450836521</v>
+        <v>-2.339716124079255</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.106293131915325</v>
       </c>
       <c r="E32">
-        <v>-22.73279176249886</v>
+        <v>-25.26688195876565</v>
       </c>
       <c r="F32">
-        <v>2.004444360778805</v>
+        <v>1.413596400118807</v>
       </c>
       <c r="G32">
-        <v>-0.2954508943457303</v>
+        <v>-2.437668650393235</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.066724805338163</v>
       </c>
       <c r="E33">
-        <v>-22.26414339660521</v>
+        <v>-24.1852694398632</v>
       </c>
       <c r="F33">
-        <v>2.04517352923965</v>
+        <v>1.373594538237618</v>
       </c>
       <c r="G33">
-        <v>0.2115530945038787</v>
+        <v>-2.22392699071879</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.973027303406647</v>
       </c>
       <c r="E34">
-        <v>-21.57276246057233</v>
+        <v>-24.32392024673128</v>
       </c>
       <c r="F34">
-        <v>1.766452749219701</v>
+        <v>1.27927165555045</v>
       </c>
       <c r="G34">
-        <v>0.1990606816354016</v>
+        <v>-2.040441250110757</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.830481834376323</v>
       </c>
       <c r="E35">
-        <v>-20.64091889525452</v>
+        <v>-24.2165846532524</v>
       </c>
       <c r="F35">
-        <v>2.250731243509542</v>
+        <v>1.186458058271182</v>
       </c>
       <c r="G35">
-        <v>-0.61398262041828</v>
+        <v>-2.191793946291368</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.643498315194997</v>
       </c>
       <c r="E36">
-        <v>-20.7425355167391</v>
+        <v>-23.12414471242613</v>
       </c>
       <c r="F36">
-        <v>1.791928360325397</v>
+        <v>1.251940501462483</v>
       </c>
       <c r="G36">
-        <v>-0.2543212240573316</v>
+        <v>-1.968416028331124</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.413044055550172</v>
       </c>
       <c r="E37">
-        <v>-20.51759343817506</v>
+        <v>-23.17196063440888</v>
       </c>
       <c r="F37">
-        <v>1.304311545402273</v>
+        <v>0.9933225415736718</v>
       </c>
       <c r="G37">
-        <v>0.6296821159828092</v>
+        <v>-1.49071503677217</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.148742587657294</v>
       </c>
       <c r="E38">
-        <v>-21.47502493846514</v>
+        <v>-22.34636036799152</v>
       </c>
       <c r="F38">
-        <v>1.399414750182879</v>
+        <v>0.7751471350243381</v>
       </c>
       <c r="G38">
-        <v>0.9687369052861005</v>
+        <v>-1.606887949587529</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.85030497294036</v>
       </c>
       <c r="E39">
-        <v>-19.5968306406719</v>
+        <v>-21.76469481552663</v>
       </c>
       <c r="F39">
-        <v>2.472435495194802</v>
+        <v>0.5619568435050517</v>
       </c>
       <c r="G39">
-        <v>0.4682649994034569</v>
+        <v>-0.713770500179812</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.524811252668939</v>
       </c>
       <c r="E40">
-        <v>-17.94425539488865</v>
+        <v>-21.45354452949312</v>
       </c>
       <c r="F40">
-        <v>1.425024556807829</v>
+        <v>0.5432274565277548</v>
       </c>
       <c r="G40">
-        <v>0.7759203635094288</v>
+        <v>-0.6200056081899784</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.17617788853017</v>
       </c>
       <c r="E41">
-        <v>-18.44638695048307</v>
+        <v>-20.8302554931308</v>
       </c>
       <c r="F41">
-        <v>1.490386058358321</v>
+        <v>0.5618665514581466</v>
       </c>
       <c r="G41">
-        <v>1.777054759629867</v>
+        <v>-0.8135897088764374</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.809289265793014</v>
       </c>
       <c r="E42">
-        <v>-17.82039832675961</v>
+        <v>-21.5933997676454</v>
       </c>
       <c r="F42">
-        <v>1.199347455058742</v>
+        <v>0.2021455216902528</v>
       </c>
       <c r="G42">
-        <v>1.413226614901502</v>
+        <v>-0.7276962118288103</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.436657590663834</v>
       </c>
       <c r="E43">
-        <v>-16.89164059745615</v>
+        <v>-19.74473895558302</v>
       </c>
       <c r="F43">
-        <v>0.8348044986391528</v>
+        <v>-0.2453708556307493</v>
       </c>
       <c r="G43">
-        <v>0.8128937284087752</v>
+        <v>-0.1495520436159554</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.062676707469508</v>
       </c>
       <c r="E44">
-        <v>-18.66045176858738</v>
+        <v>-19.55630360456422</v>
       </c>
       <c r="F44">
-        <v>1.427826095364096</v>
+        <v>-0.01556102890909647</v>
       </c>
       <c r="G44">
-        <v>1.66695966022262</v>
+        <v>-0.43113651223507</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.701749781430421</v>
       </c>
       <c r="E45">
-        <v>-17.52705701088697</v>
+        <v>-20.24311185492847</v>
       </c>
       <c r="F45">
-        <v>0.640658373710227</v>
+        <v>-0.3059882970654088</v>
       </c>
       <c r="G45">
-        <v>1.600751177391987</v>
+        <v>0.1003954220480483</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.361163787551451</v>
       </c>
       <c r="E46">
-        <v>-16.39045182083247</v>
+        <v>-19.46695556933319</v>
       </c>
       <c r="F46">
-        <v>1.065985273412439</v>
+        <v>-0.1188667277122228</v>
       </c>
       <c r="G46">
-        <v>1.207714022178246</v>
+        <v>-0.4449656263341971</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.05281762083796</v>
       </c>
       <c r="E47">
-        <v>-15.47808266341679</v>
+        <v>-19.00625229670393</v>
       </c>
       <c r="F47">
-        <v>0.5987554086396141</v>
+        <v>-0.3623404747430535</v>
       </c>
       <c r="G47">
-        <v>2.345118842976434</v>
+        <v>-0.8720155620809616</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.788726978612299</v>
       </c>
       <c r="E48">
-        <v>-15.47919572405184</v>
+        <v>-18.47797627581971</v>
       </c>
       <c r="F48">
-        <v>0.5980686920626933</v>
+        <v>-0.4728745075030084</v>
       </c>
       <c r="G48">
-        <v>1.338230365777182</v>
+        <v>-0.6952054953924055</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.574558219895579</v>
       </c>
       <c r="E49">
-        <v>-15.31182546087257</v>
+        <v>-18.52094540018639</v>
       </c>
       <c r="F49">
-        <v>1.345768020442778</v>
+        <v>-0.4256890435047429</v>
       </c>
       <c r="G49">
-        <v>0.6932041426291865</v>
+        <v>-0.8916092002372669</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.422226302800156</v>
       </c>
       <c r="E50">
-        <v>-16.05983128010817</v>
+        <v>-17.67223251274635</v>
       </c>
       <c r="F50">
-        <v>0.7414640596917045</v>
+        <v>-0.783685412340008</v>
       </c>
       <c r="G50">
-        <v>0.3020676094777763</v>
+        <v>-0.3735095468754264</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.331588056701435</v>
       </c>
       <c r="E51">
-        <v>-14.07694698444998</v>
+        <v>-18.51523058140343</v>
       </c>
       <c r="F51">
-        <v>1.013973740925463</v>
+        <v>-0.6582366244926481</v>
       </c>
       <c r="G51">
-        <v>1.213964144729371</v>
+        <v>-0.648896107835238</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.30671081058019</v>
       </c>
       <c r="E52">
-        <v>-15.21724022616093</v>
+        <v>-16.38714171140658</v>
       </c>
       <c r="F52">
-        <v>0.817781548511623</v>
+        <v>-0.9004794175629187</v>
       </c>
       <c r="G52">
-        <v>0.6067388925161057</v>
+        <v>-0.7545398877146371</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.343148366820307</v>
       </c>
       <c r="E53">
-        <v>-13.73830243944611</v>
+        <v>-17.70909226325421</v>
       </c>
       <c r="F53">
-        <v>0.7821120481470762</v>
+        <v>-1.164510758429025</v>
       </c>
       <c r="G53">
-        <v>0.286204725342172</v>
+        <v>-1.084864347105246</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.435533580348342</v>
       </c>
       <c r="E54">
-        <v>-13.88479035608414</v>
+        <v>-17.186506141885</v>
       </c>
       <c r="F54">
-        <v>0.8987842833617754</v>
+        <v>-1.064222802074297</v>
       </c>
       <c r="G54">
-        <v>-0.4133625630587707</v>
+        <v>-0.7738150150308265</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.578612015786975</v>
       </c>
       <c r="E55">
-        <v>-13.22644406292894</v>
+        <v>-17.50578010926987</v>
       </c>
       <c r="F55">
-        <v>0.3420716866363397</v>
+        <v>-1.081885251836788</v>
       </c>
       <c r="G55">
-        <v>-0.3745903951361473</v>
+        <v>-1.180686505832877</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.760419353031417</v>
       </c>
       <c r="E56">
-        <v>-12.33449624559744</v>
+        <v>-16.30477522441258</v>
       </c>
       <c r="F56">
-        <v>0.4549847905771347</v>
+        <v>-1.384485378977239</v>
       </c>
       <c r="G56">
-        <v>-0.2136197158818754</v>
+        <v>-1.578509155882128</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-1.975216976109959</v>
       </c>
       <c r="E57">
-        <v>-13.04635251346173</v>
+        <v>-16.89702731254446</v>
       </c>
       <c r="F57">
-        <v>0.1651696859314913</v>
+        <v>-1.346286872931945</v>
       </c>
       <c r="G57">
-        <v>-0.09834750995045055</v>
+        <v>-1.599429052290719</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.209163538737299</v>
       </c>
       <c r="E58">
-        <v>-12.870742279014</v>
+        <v>-16.96036793845942</v>
       </c>
       <c r="F58">
-        <v>0.1886845513947608</v>
+        <v>-1.318622715148053</v>
       </c>
       <c r="G58">
-        <v>0.1907219634113858</v>
+        <v>-1.570173048402703</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.455795374746643</v>
       </c>
       <c r="E59">
-        <v>-11.51305334371622</v>
+        <v>-16.85409972029103</v>
       </c>
       <c r="F59">
-        <v>-0.4609427034330842</v>
+        <v>-1.610722457090618</v>
       </c>
       <c r="G59">
-        <v>-0.9511080694687386</v>
+        <v>-0.9885487576498942</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.705568859000068</v>
       </c>
       <c r="E60">
-        <v>-12.78415612931397</v>
+        <v>-16.68915493252546</v>
       </c>
       <c r="F60">
-        <v>-0.7774063874267878</v>
+        <v>-1.783763437331018</v>
       </c>
       <c r="G60">
-        <v>-1.317079635506408</v>
+        <v>-1.332522189762843</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.950580718836664</v>
       </c>
       <c r="E61">
-        <v>-11.13887807582845</v>
+        <v>-17.13091540830218</v>
       </c>
       <c r="F61">
-        <v>-0.2194073361248044</v>
+        <v>-1.665639074059211</v>
       </c>
       <c r="G61">
-        <v>-1.262214837924162</v>
+        <v>-1.98899652794287</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.18858691227285</v>
       </c>
       <c r="E62">
-        <v>-14.0328897187162</v>
+        <v>-15.88546700905789</v>
       </c>
       <c r="F62">
-        <v>-0.69188076655735</v>
+        <v>-1.902987872513742</v>
       </c>
       <c r="G62">
-        <v>-1.130800398185884</v>
+        <v>-1.980140882289813</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.413193906481159</v>
       </c>
       <c r="E63">
-        <v>-11.92361904923215</v>
+        <v>-16.19337779025803</v>
       </c>
       <c r="F63">
-        <v>-0.05848040078294445</v>
+        <v>-1.979905099333287</v>
       </c>
       <c r="G63">
-        <v>-1.194045685905603</v>
+        <v>-1.621260098561608</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.627169605812645</v>
       </c>
       <c r="E64">
-        <v>-11.45649075868339</v>
+        <v>-15.76069208122607</v>
       </c>
       <c r="F64">
-        <v>-0.03963835583886689</v>
+        <v>-2.169136520461404</v>
       </c>
       <c r="G64">
-        <v>-1.886858978049336</v>
+        <v>-1.687416366500419</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.827415100676292</v>
       </c>
       <c r="E65">
-        <v>-11.41371268203765</v>
+        <v>-15.20446079491443</v>
       </c>
       <c r="F65">
-        <v>-0.4485337597391477</v>
+        <v>-2.220173064515284</v>
       </c>
       <c r="G65">
-        <v>-1.139520285120202</v>
+        <v>-1.793475254769805</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.015856852415172</v>
       </c>
       <c r="E66">
-        <v>-11.31412282767959</v>
+        <v>-16.87955059928958</v>
       </c>
       <c r="F66">
-        <v>-0.6875053299357631</v>
+        <v>-2.14450501573916</v>
       </c>
       <c r="G66">
-        <v>-1.484026309129738</v>
+        <v>-2.222906189583665</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.194342662800612</v>
       </c>
       <c r="E67">
-        <v>-11.57167176835486</v>
+        <v>-16.05833197081991</v>
       </c>
       <c r="F67">
-        <v>-0.7173944825635747</v>
+        <v>-2.679385161196412</v>
       </c>
       <c r="G67">
-        <v>-1.272161774816304</v>
+        <v>-1.842880985412032</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.359974023914122</v>
       </c>
       <c r="E68">
-        <v>-11.86868867624997</v>
+        <v>-15.85016055958553</v>
       </c>
       <c r="F68">
-        <v>-0.8281206965609791</v>
+        <v>-2.452808452447886</v>
       </c>
       <c r="G68">
-        <v>-1.565766111532904</v>
+        <v>-1.928429864173633</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.516396761541698</v>
       </c>
       <c r="E69">
-        <v>-11.29537107854799</v>
+        <v>-15.83964047529973</v>
       </c>
       <c r="F69">
-        <v>-0.8603425317950743</v>
+        <v>-2.582119089127097</v>
       </c>
       <c r="G69">
-        <v>-0.6586159099479528</v>
+        <v>-1.831187460388436</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.657256621984697</v>
       </c>
       <c r="E70">
-        <v>-12.43585121476855</v>
+        <v>-15.76409771451243</v>
       </c>
       <c r="F70">
-        <v>-0.8552049971629118</v>
+        <v>-2.522700295324289</v>
       </c>
       <c r="G70">
-        <v>-2.093233116487659</v>
+        <v>-2.488290988014921</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.784134227700672</v>
       </c>
       <c r="E71">
-        <v>-12.88360892769832</v>
+        <v>-15.78367595269767</v>
       </c>
       <c r="F71">
-        <v>-1.122777608675986</v>
+        <v>-2.649227617530094</v>
       </c>
       <c r="G71">
-        <v>-0.256174852717022</v>
+        <v>-2.173244605971508</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.894830557071423</v>
       </c>
       <c r="E72">
-        <v>-11.95235927159996</v>
+        <v>-16.47065448472623</v>
       </c>
       <c r="F72">
-        <v>-1.041663044226455</v>
+        <v>-2.910231275538967</v>
       </c>
       <c r="G72">
-        <v>-0.815793177311337</v>
+        <v>-2.07757125968557</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.986145284808255</v>
       </c>
       <c r="E73">
-        <v>-13.97609040063784</v>
+        <v>-16.01027100936899</v>
       </c>
       <c r="F73">
-        <v>-1.445878172300919</v>
+        <v>-2.800470937933227</v>
       </c>
       <c r="G73">
-        <v>-0.2481598668223042</v>
+        <v>-1.981686443087753</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.062223019293242</v>
       </c>
       <c r="E74">
-        <v>-11.79811730941848</v>
+        <v>-16.477606960484</v>
       </c>
       <c r="F74">
-        <v>-1.211296120971738</v>
+        <v>-3.08672323437943</v>
       </c>
       <c r="G74">
-        <v>-2.3956095550304</v>
+        <v>-2.485272967267594</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.117937042884953</v>
       </c>
       <c r="E75">
-        <v>-13.0172592681313</v>
+        <v>-16.72021264681253</v>
       </c>
       <c r="F75">
-        <v>-1.247970430995881</v>
+        <v>-2.883522225370503</v>
       </c>
       <c r="G75">
-        <v>-0.9935953269445162</v>
+        <v>-2.063402748789598</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.158325465539905</v>
       </c>
       <c r="E76">
-        <v>-14.20229505544463</v>
+        <v>-17.26628517822364</v>
       </c>
       <c r="F76">
-        <v>-1.019594508248474</v>
+        <v>-2.578260553764857</v>
       </c>
       <c r="G76">
-        <v>-0.7217254389489343</v>
+        <v>-2.289059846777884</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.181676447896997</v>
       </c>
       <c r="E77">
-        <v>-12.97946919828669</v>
+        <v>-17.37991704007095</v>
       </c>
       <c r="F77">
-        <v>-1.23963788329112</v>
+        <v>-2.685336980985527</v>
       </c>
       <c r="G77">
-        <v>-1.028164196075447</v>
+        <v>-1.768002219794312</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.188689466990475</v>
       </c>
       <c r="E78">
-        <v>-14.01462804852093</v>
+        <v>-18.25068347964582</v>
       </c>
       <c r="F78">
-        <v>-1.264724990084903</v>
+        <v>-2.617977457259482</v>
       </c>
       <c r="G78">
-        <v>-0.8206204440603055</v>
+        <v>-1.762973925711828</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.184734493383886</v>
       </c>
       <c r="E79">
-        <v>-14.64037163277622</v>
+        <v>-18.11191222964933</v>
       </c>
       <c r="F79">
-        <v>-1.359400757285664</v>
+        <v>-2.756223693112692</v>
       </c>
       <c r="G79">
-        <v>-0.1966054933815902</v>
+        <v>-1.489440993411707</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.167264152719948</v>
       </c>
       <c r="E80">
-        <v>-14.82524768168964</v>
+        <v>-19.40173353868808</v>
       </c>
       <c r="F80">
-        <v>-1.22781956555538</v>
+        <v>-2.768926707234622</v>
       </c>
       <c r="G80">
-        <v>-0.152906850415536</v>
+        <v>-1.947073191298773</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.14583262187011</v>
       </c>
       <c r="E81">
-        <v>-15.46758334518762</v>
+        <v>-20.2465465606941</v>
       </c>
       <c r="F81">
-        <v>-1.302935921641239</v>
+        <v>-2.943027997750605</v>
       </c>
       <c r="G81">
-        <v>0.0616389185929716</v>
+        <v>-1.487710069747799</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.119198061596104</v>
       </c>
       <c r="E82">
-        <v>-18.41191529648699</v>
+        <v>-20.91409221693379</v>
       </c>
       <c r="F82">
-        <v>-1.057503085702787</v>
+        <v>-2.477375344512711</v>
       </c>
       <c r="G82">
-        <v>0.04554106744416708</v>
+        <v>-2.135639440881112</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.096377816254864</v>
       </c>
       <c r="E83">
-        <v>-18.40489636934803</v>
+        <v>-22.46076472714524</v>
       </c>
       <c r="F83">
-        <v>-1.636077126555505</v>
+        <v>-2.491950468964968</v>
       </c>
       <c r="G83">
-        <v>0.2887815302536008</v>
+        <v>-1.143052622551979</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.083472173602221</v>
       </c>
       <c r="E84">
-        <v>-18.46432882340633</v>
+        <v>-22.9547726013883</v>
       </c>
       <c r="F84">
-        <v>-1.717576053479934</v>
+        <v>-2.725881423515549</v>
       </c>
       <c r="G84">
-        <v>-0.08456538925396352</v>
+        <v>-1.411264857375411</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.082702281791746</v>
       </c>
       <c r="E85">
-        <v>-19.68944725321558</v>
+        <v>-24.00998315589881</v>
       </c>
       <c r="F85">
-        <v>-1.407856108512421</v>
+        <v>-2.829752897254787</v>
       </c>
       <c r="G85">
-        <v>0.1283225569391871</v>
+        <v>-0.9064565047269281</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.107981002156581</v>
       </c>
       <c r="E86">
-        <v>-21.25355909777998</v>
+        <v>-25.15442130251194</v>
       </c>
       <c r="F86">
-        <v>-1.646336456839177</v>
+        <v>-2.306401140942296</v>
       </c>
       <c r="G86">
-        <v>0.9254142095411666</v>
+        <v>-0.5767116306355468</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.159012455604396</v>
       </c>
       <c r="E87">
-        <v>-21.97686992247814</v>
+        <v>-26.50422328950387</v>
       </c>
       <c r="F87">
-        <v>-1.167777839465666</v>
+        <v>-2.297032305616633</v>
       </c>
       <c r="G87">
-        <v>0.3093776943328935</v>
+        <v>-0.7993820368115989</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-5.249917766458931</v>
       </c>
       <c r="E88">
-        <v>-23.20299758263933</v>
+        <v>-26.88675897178852</v>
       </c>
       <c r="F88">
-        <v>-1.039369294888103</v>
+        <v>-2.198584981630926</v>
       </c>
       <c r="G88">
-        <v>-0.06747806590512706</v>
+        <v>-1.251424630529091</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-5.382722393189441</v>
       </c>
       <c r="E89">
-        <v>-24.56812907263119</v>
+        <v>-28.96715236293104</v>
       </c>
       <c r="F89">
-        <v>-1.520020368321086</v>
+        <v>-2.250416758391494</v>
       </c>
       <c r="G89">
-        <v>0.7405891569578927</v>
+        <v>-0.9523246764481974</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.562883985781947</v>
       </c>
       <c r="E90">
-        <v>-28.13359662022096</v>
+        <v>-29.88565166026217</v>
       </c>
       <c r="F90">
-        <v>-1.229366127496407</v>
+        <v>-2.098671447342264</v>
       </c>
       <c r="G90">
-        <v>1.000478338024856</v>
+        <v>-1.387175517033209</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.800472485773759</v>
       </c>
       <c r="E91">
-        <v>-29.75526159071918</v>
+        <v>-31.74831087109488</v>
       </c>
       <c r="F91">
-        <v>-1.279500579448638</v>
+        <v>-2.260088776186581</v>
       </c>
       <c r="G91">
-        <v>1.406227208652727</v>
+        <v>-0.8729789268350825</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.091639430085092</v>
       </c>
       <c r="E92">
-        <v>-31.38332873647461</v>
+        <v>-32.78274498595294</v>
       </c>
       <c r="F92">
-        <v>-0.8486186479432529</v>
+        <v>-1.738032586492068</v>
       </c>
       <c r="G92">
-        <v>1.11326250436095</v>
+        <v>-1.176522368210051</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.449982204324869</v>
       </c>
       <c r="E93">
-        <v>-33.26837583295382</v>
+        <v>-35.70436094791116</v>
       </c>
       <c r="F93">
-        <v>-0.8909896405964476</v>
+        <v>-1.749411869504325</v>
       </c>
       <c r="G93">
-        <v>0.7234078468037761</v>
+        <v>-1.402907863939257</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.866442818002538</v>
       </c>
       <c r="E94">
-        <v>-33.56590981565887</v>
+        <v>-37.26947163979919</v>
       </c>
       <c r="F94">
-        <v>-0.9199982386750835</v>
+        <v>-1.851092311463159</v>
       </c>
       <c r="G94">
-        <v>1.14227048751281</v>
+        <v>-1.861247573610515</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.34685085296343</v>
       </c>
       <c r="E95">
-        <v>-36.94531349589632</v>
+        <v>-40.06065600010118</v>
       </c>
       <c r="F95">
-        <v>-1.218144234290682</v>
+        <v>-2.070680912801668</v>
       </c>
       <c r="G95">
-        <v>0.4432201265409072</v>
+        <v>-2.107511278656458</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-7.891153909107879</v>
       </c>
       <c r="E96">
-        <v>-38.94763066734338</v>
+        <v>-41.30386166523005</v>
       </c>
       <c r="F96">
-        <v>-1.631609741152207</v>
+        <v>-1.984982163145045</v>
       </c>
       <c r="G96">
-        <v>-0.2890650130758672</v>
+        <v>-1.992017159434788</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.481081758194492</v>
       </c>
       <c r="E97">
-        <v>-41.44676328388909</v>
+        <v>-43.63831322292931</v>
       </c>
       <c r="F97">
-        <v>-1.142276548970483</v>
+        <v>-1.905253457360399</v>
       </c>
       <c r="G97">
-        <v>0.2268729437645315</v>
+        <v>-1.883470231570071</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.127352437043459</v>
       </c>
       <c r="E98">
-        <v>-43.31502725340466</v>
+        <v>-45.28604374770215</v>
       </c>
       <c r="F98">
-        <v>-1.480118738895636</v>
+        <v>-1.853290798550189</v>
       </c>
       <c r="G98">
-        <v>-0.8052875410766972</v>
+        <v>-2.085095425597159</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.786909060769826</v>
       </c>
       <c r="E99">
-        <v>-45.97923652217549</v>
+        <v>-47.40615949025815</v>
       </c>
       <c r="F99">
-        <v>-1.596409096737645</v>
+        <v>-1.595672678116556</v>
       </c>
       <c r="G99">
-        <v>-0.7417655144303198</v>
+        <v>-2.233975746649985</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.48223619968891</v>
       </c>
       <c r="E100">
-        <v>-47.87467599169225</v>
+        <v>-49.40869470529977</v>
       </c>
       <c r="F100">
-        <v>-1.677181545449819</v>
+        <v>-1.883186578117223</v>
       </c>
       <c r="G100">
-        <v>-0.5315588029322426</v>
+        <v>-2.306233324698227</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.14174307117562</v>
       </c>
       <c r="E101">
-        <v>-49.96078731652622</v>
+        <v>-51.26377430546468</v>
       </c>
       <c r="F101">
-        <v>-2.018975047886326</v>
+        <v>-1.930430027833684</v>
       </c>
       <c r="G101">
-        <v>-1.380217882697892</v>
+        <v>-2.506158923996501</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.82253221815681</v>
       </c>
       <c r="E102">
-        <v>-50.69659411579796</v>
+        <v>-52.8225035881521</v>
       </c>
       <c r="F102">
-        <v>-2.063069044737344</v>
+        <v>-2.171833684724919</v>
       </c>
       <c r="G102">
-        <v>-1.20393518641674</v>
+        <v>-3.19774516618241</v>
       </c>
     </row>
   </sheetData>
